--- a/data/trans_orig/Q5414-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5414-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2007</t>
+          <t>Población según si es capaz de comer solo en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7868</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2343</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8061</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8240</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2343</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107933</t>
+          <t>107740</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114125</t>
+          <t>114130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141474</t>
+          <t>141667</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>254266</t>
+          <t>253200</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>262789</t>
+          <t>262699</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15015</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137323</t>
+          <t>136491</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144958</t>
+          <t>144928</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>172361</t>
+          <t>171774</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181542</t>
+          <t>181549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>313553</t>
+          <t>313351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>325264</t>
+          <t>324648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,62 +1680,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>5585</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1758,97 +1758,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7259</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6551</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7433</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7472</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>99466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129299</t>
+          <t>128591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231114</t>
+          <t>231961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239237</t>
+          <t>239238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>840</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131192</t>
+          <t>130524</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137217</t>
+          <t>136407</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>198427</t>
+          <t>198671</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207689</t>
+          <t>207658</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>332360</t>
+          <t>333601</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>343178</t>
+          <t>343201</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26306</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>484502</t>
+          <t>484991</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>497122</t>
+          <t>496990</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,49 +2798,49 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>663783</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>655807</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>669677</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>96,89%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
           <t>98,94%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>663783</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>655489</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>670437</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1160</t>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1145491</t>
+          <t>1145012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1164476</t>
+          <t>1164796</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2012</t>
+          <t>Población según si es capaz de comer solo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129776</t>
+          <t>129601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138484</t>
+          <t>138475</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>156626</t>
+          <t>157225</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165730</t>
+          <t>165726</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>290094</t>
+          <t>290388</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>302150</t>
+          <t>302188</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>15069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15967</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144702</t>
+          <t>144397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153832</t>
+          <t>153800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171571</t>
+          <t>171833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185821</t>
+          <t>185615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>321146</t>
+          <t>321237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337495</t>
+          <t>337588</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14962</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89659</t>
+          <t>89764</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102454</t>
+          <t>101580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123479</t>
+          <t>123514</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137272</t>
+          <t>137419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218464</t>
+          <t>220227</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>236615</t>
+          <t>236956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13676</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>20487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>147200</t>
+          <t>147846</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>159582</t>
+          <t>159584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>225492</t>
+          <t>225754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>238436</t>
+          <t>238517</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>378274</t>
+          <t>379093</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>396047</t>
+          <t>395733</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>22159</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30127</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13617</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>33545</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50579</t>
+          <t>50461</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>527334</t>
+          <t>528178</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>547274</t>
+          <t>547452</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>693928</t>
+          <t>694417</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>718352</t>
+          <t>718993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1229100</t>
+          <t>1228696</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1260517</t>
+          <t>1260631</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2016</t>
+          <t>Población según si es capaz de comer solo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,97 +5757,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1194</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1760</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5888</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1194</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4864</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1194</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5989</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17092</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128931</t>
+          <t>128496</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135921</t>
+          <t>135890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158647</t>
+          <t>159878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170128</t>
+          <t>170979</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>291560</t>
+          <t>291869</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>304773</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13292</t>
+          <t>13298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155339</t>
+          <t>155320</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163254</t>
+          <t>163247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202890</t>
+          <t>204362</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>216590</t>
+          <t>216838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>364205</t>
+          <t>362186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>378741</t>
+          <t>378441</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14732</t>
+          <t>14917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109216</t>
+          <t>109790</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123676</t>
+          <t>123421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137704</t>
+          <t>137388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>236002</t>
+          <t>235730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252243</t>
+          <t>252184</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -7125,82 +7125,82 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4991</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1233</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6272</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170023</t>
+          <t>170792</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>228675</t>
+          <t>228377</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>240176</t>
+          <t>240258</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>403118</t>
+          <t>402158</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>414821</t>
+          <t>414715</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19466</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20181</t>
+          <t>19902</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33994</t>
+          <t>33473</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20709</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43453</t>
+          <t>42659</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>575425</t>
+          <t>574837</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>586341</t>
+          <t>586254</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>733836</t>
+          <t>733540</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>757364</t>
+          <t>757465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1315238</t>
+          <t>1315140</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1341109</t>
+          <t>1340787</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2023</t>
+          <t>Población según si es capaz de comer solo en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>336</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>142307</t>
+          <t>141605</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146898</t>
+          <t>146794</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>166851</t>
+          <t>167017</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>174083</t>
+          <t>173735</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>311625</t>
+          <t>311191</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>319938</t>
+          <t>319752</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151652</t>
+          <t>151535</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158325</t>
+          <t>158087</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202844</t>
+          <t>202577</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211965</t>
+          <t>211898</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>357310</t>
+          <t>357118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>368493</t>
+          <t>368506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -9181,97 +9181,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4729</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1313</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5063</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>5536</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>9126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132684</t>
+          <t>132564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347049</t>
+          <t>347646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359719</t>
+          <t>359565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>485589</t>
+          <t>485723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>496245</t>
+          <t>496403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15744</t>
+          <t>15809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>197145</t>
+          <t>196498</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>203685</t>
+          <t>203288</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>262083</t>
+          <t>262868</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>271270</t>
+          <t>271219</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>462398</t>
+          <t>462971</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>472890</t>
+          <t>473657</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,82 +10108,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>7576</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3392</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>12143</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>10356</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>5906</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>15602</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>0,93%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>7576</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>3518</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>12425</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>10356</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>5848</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>16012</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14802</t>
+          <t>14647</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,39 +10221,39 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>23569</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>11771</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>34088</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>23569</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>11833</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>34013</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44729</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>631943</t>
+          <t>632311</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>642708</t>
+          <t>642709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>990125</t>
+          <t>990126</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1017981</t>
+          <t>1017881</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1628130</t>
+          <t>1628340</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1655366</t>
+          <t>1655615</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5414-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5414-Habitat-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107740</t>
+          <t>107870</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114130</t>
+          <t>114138</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141667</t>
+          <t>141728</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>253200</t>
+          <t>253372</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>262699</t>
+          <t>262712</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10906</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136491</t>
+          <t>136859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144928</t>
+          <t>144949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171774</t>
+          <t>171657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181549</t>
+          <t>181531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>313351</t>
+          <t>313440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>324648</t>
+          <t>324918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99466</t>
+          <t>99425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128591</t>
+          <t>128326</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231961</t>
+          <t>232071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239238</t>
+          <t>239245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>832</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130524</t>
+          <t>130580</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136407</t>
+          <t>136419</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>198671</t>
+          <t>198322</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207658</t>
+          <t>207647</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>333601</t>
+          <t>333086</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>343201</t>
+          <t>343269</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>484991</t>
+          <t>486132</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>496990</t>
+          <t>497134</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>655807</t>
+          <t>654809</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>669677</t>
+          <t>669963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1145012</t>
+          <t>1145656</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1164796</t>
+          <t>1164511</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11493</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129601</t>
+          <t>129579</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138475</t>
+          <t>138503</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>157225</t>
+          <t>157150</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165726</t>
+          <t>165721</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>290388</t>
+          <t>290355</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>302188</t>
+          <t>302143</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3834,77 +3834,77 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2367</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>13635</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>14894</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>4,3%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>6780</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>3174</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>15069</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>7892</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>15615</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144397</t>
+          <t>145326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153800</t>
+          <t>153869</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171833</t>
+          <t>171420</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185615</t>
+          <t>185815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>321237</t>
+          <t>322208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337588</t>
+          <t>337904</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12851</t>
+          <t>13614</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21154</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89764</t>
+          <t>89528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101580</t>
+          <t>102473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123514</t>
+          <t>124078</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137419</t>
+          <t>137409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>220227</t>
+          <t>220644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>236956</t>
+          <t>236967</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12649</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,47 +4741,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6177</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>13477</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>6177</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2097</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>12488</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20487</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>147846</t>
+          <t>146699</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>159584</t>
+          <t>159544</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>225754</t>
+          <t>225059</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>238517</t>
+          <t>238584</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>379093</t>
+          <t>378495</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>395733</t>
+          <t>396119</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>22027</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>30060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>25538</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33545</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>49583</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>528178</t>
+          <t>527851</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>547452</t>
+          <t>547199</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>694417</t>
+          <t>694184</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>718993</t>
+          <t>718532</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1228696</t>
+          <t>1231346</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1260631</t>
+          <t>1262104</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>817</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128496</t>
+          <t>128155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135890</t>
+          <t>135917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>159878</t>
+          <t>159673</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170979</t>
+          <t>170931</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>291869</t>
+          <t>291754</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>304359</t>
+          <t>304929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13298</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155320</t>
+          <t>155452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163247</t>
+          <t>163231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204362</t>
+          <t>203831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>216838</t>
+          <t>216799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>362186</t>
+          <t>364605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>378441</t>
+          <t>378564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>10762</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>16389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109790</t>
+          <t>110597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123421</t>
+          <t>122914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137388</t>
+          <t>137579</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235730</t>
+          <t>235878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252184</t>
+          <t>252237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170792</t>
+          <t>170790</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>228377</t>
+          <t>227546</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>240258</t>
+          <t>240234</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>402158</t>
+          <t>401577</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>414715</t>
+          <t>414612</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18940</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19902</t>
+          <t>18668</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33473</t>
+          <t>33711</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20157</t>
+          <t>20554</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>43067</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>574837</t>
+          <t>574420</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>586254</t>
+          <t>586161</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>733540</t>
+          <t>733546</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>757465</t>
+          <t>757487</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1315140</t>
+          <t>1314051</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1340787</t>
+          <t>1341043</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8274,22 +8274,22 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>12683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>145003</t>
+          <t>160277</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141605</t>
+          <t>157149</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146794</t>
+          <t>161882</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>171103</t>
+          <t>182694</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>167017</t>
+          <t>178411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>173735</t>
+          <t>185969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>316106</t>
+          <t>342971</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>311191</t>
+          <t>337838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>319752</t>
+          <t>346735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>13421</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>17724</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>155950</t>
+          <t>174028</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151535</t>
+          <t>169469</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158087</t>
+          <t>176384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>207912</t>
+          <t>230701</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202577</t>
+          <t>224925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211898</t>
+          <t>234710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>363862</t>
+          <t>404728</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>357118</t>
+          <t>398073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>368506</t>
+          <t>409963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -9402,27 +9402,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>136087</t>
+          <t>158859</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132564</t>
+          <t>156009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>355806</t>
+          <t>170232</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347646</t>
+          <t>165479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359565</t>
+          <t>173013</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>491894</t>
+          <t>329091</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>485723</t>
+          <t>324429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>496403</t>
+          <t>332142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>401</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,22 +9702,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>453</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>11753</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>20548</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>201144</t>
+          <t>210831</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>196498</t>
+          <t>206193</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>203288</t>
+          <t>213183</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>267821</t>
+          <t>285995</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>262868</t>
+          <t>278820</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>271219</t>
+          <t>290109</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>468965</t>
+          <t>496824</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>462971</t>
+          <t>488603</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>473657</t>
+          <t>501975</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11771</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34088</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>32785</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43678</t>
+          <t>45972</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>638183</t>
+          <t>703994</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>632311</t>
+          <t>697248</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>642709</t>
+          <t>708509</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1002644</t>
+          <t>869621</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>990126</t>
+          <t>860507</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1017881</t>
+          <t>877457</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1640828</t>
+          <t>1573615</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1628340</t>
+          <t>1562182</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1655615</t>
+          <t>1582616</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
